--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_los_rios.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_los_rios.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.00211632620119</v>
+      </c>
+      <c r="C2">
         <v>31.63548971429596</v>
-      </c>
-      <c r="C2">
-        <v>26.00211632620119</v>
       </c>
       <c r="D2">
         <v>3.161006859799308</v>
       </c>
       <c r="E2">
-        <v>20.06849159214508</v>
+        <v>16.49486881925956</v>
       </c>
       <c r="F2">
         <v>63.43663958859536</v>
       </c>
       <c r="G2">
-        <v>16.49486881925956</v>
+        <v>20.06849159214508</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>31.31672597864769</v>
+      </c>
+      <c r="C3">
         <v>41.7987706243934</v>
-      </c>
-      <c r="C3">
-        <v>31.31672597864769</v>
       </c>
       <c r="D3">
         <v>2.392414860681114</v>
       </c>
       <c r="E3">
-        <v>24.14501962250047</v>
+        <v>18.0900766211923</v>
       </c>
       <c r="F3">
         <v>57.76490375630723</v>
       </c>
       <c r="G3">
-        <v>18.0900766211923</v>
+        <v>24.14501962250047</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>29.91734143049932</v>
+      </c>
+      <c r="C4">
         <v>35.8468286099865</v>
-      </c>
-      <c r="C4">
-        <v>29.91734143049932</v>
       </c>
       <c r="D4">
         <v>2.78964705882353</v>
       </c>
       <c r="E4">
-        <v>21.62519717091538</v>
+        <v>18.04813514476161</v>
       </c>
       <c r="F4">
         <v>60.326667684323</v>
       </c>
       <c r="G4">
-        <v>18.04813514476161</v>
+        <v>21.62519717091538</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>29.8731832430892</v>
+      </c>
+      <c r="C5">
         <v>34.66087204331718</v>
-      </c>
-      <c r="C5">
-        <v>29.8731832430892</v>
       </c>
       <c r="D5">
         <v>2.885097636176773</v>
       </c>
       <c r="E5">
+        <v>18.15623105568546</v>
+      </c>
+      <c r="F5">
+        <v>60.77769117519702</v>
+      </c>
+      <c r="G5">
         <v>21.06607776911752</v>
-      </c>
-      <c r="F5">
-        <v>60.77769117519703</v>
-      </c>
-      <c r="G5">
-        <v>18.15623105568546</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.16500994035785</v>
+      </c>
+      <c r="C6">
         <v>35.46719681908549</v>
-      </c>
-      <c r="C6">
-        <v>29.16500994035785</v>
       </c>
       <c r="D6">
         <v>2.819506726457399</v>
       </c>
       <c r="E6">
+        <v>17.71525178118584</v>
+      </c>
+      <c r="F6">
+        <v>60.74145634585194</v>
+      </c>
+      <c r="G6">
         <v>21.5432918729622</v>
-      </c>
-      <c r="F6">
-        <v>60.74145634585195</v>
-      </c>
-      <c r="G6">
-        <v>17.71525178118585</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>33.27395091053048</v>
+      </c>
+      <c r="C7">
         <v>31.54526260226973</v>
-      </c>
-      <c r="C7">
-        <v>33.27395091053048</v>
       </c>
       <c r="D7">
         <v>3.170048107090567</v>
       </c>
       <c r="E7">
-        <v>19.13931144915933</v>
+        <v>20.18815052041633</v>
       </c>
       <c r="F7">
         <v>60.67253803042433</v>
       </c>
       <c r="G7">
-        <v>20.18815052041633</v>
+        <v>19.13931144915933</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>29.57601587184951</v>
+      </c>
+      <c r="C8">
         <v>37.51928870600338</v>
-      </c>
-      <c r="C8">
-        <v>29.57601587184951</v>
       </c>
       <c r="D8">
         <v>2.665295730513122</v>
       </c>
       <c r="E8">
-        <v>22.45382585751979</v>
+        <v>17.70008795074758</v>
       </c>
       <c r="F8">
         <v>59.84608619173263</v>
       </c>
       <c r="G8">
-        <v>17.70008795074758</v>
+        <v>22.45382585751979</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>29.89227650355766</v>
+      </c>
+      <c r="C9">
         <v>33.14783161744246</v>
-      </c>
-      <c r="C9">
-        <v>29.89227650355766</v>
       </c>
       <c r="D9">
         <v>3.016788583763041</v>
       </c>
       <c r="E9">
+        <v>18.33430856251219</v>
+      </c>
+      <c r="F9">
+        <v>61.33460113126585</v>
+      </c>
+      <c r="G9">
         <v>20.33109030622196</v>
-      </c>
-      <c r="F9">
-        <v>61.33460113126583</v>
-      </c>
-      <c r="G9">
-        <v>18.33430856251218</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.09342452976838</v>
+      </c>
+      <c r="C10">
         <v>36.86849059536764</v>
-      </c>
-      <c r="C10">
-        <v>28.09342452976838</v>
       </c>
       <c r="D10">
         <v>2.712343206493096</v>
       </c>
       <c r="E10">
-        <v>22.34969845457972</v>
+        <v>17.03024877497173</v>
       </c>
       <c r="F10">
         <v>60.62005277044855</v>
       </c>
       <c r="G10">
-        <v>17.03024877497173</v>
+        <v>22.34969845457972</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>32.30626450116009</v>
+      </c>
+      <c r="C11">
         <v>32.67749419953596</v>
-      </c>
-      <c r="C11">
-        <v>32.30626450116009</v>
       </c>
       <c r="D11">
         <v>3.060210167566032</v>
       </c>
       <c r="E11">
-        <v>19.80649153400461</v>
+        <v>19.58148168982393</v>
       </c>
       <c r="F11">
         <v>60.61202677617145</v>
       </c>
       <c r="G11">
-        <v>19.58148168982393</v>
+        <v>19.80649153400461</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.40360610263523</v>
+      </c>
+      <c r="C12">
         <v>37.62829403606103</v>
-      </c>
-      <c r="C12">
-        <v>29.40360610263523</v>
       </c>
       <c r="D12">
         <v>2.657574640619241</v>
       </c>
       <c r="E12">
-        <v>22.52760939965125</v>
+        <v>17.60358714605995</v>
       </c>
       <c r="F12">
         <v>59.8688034542888</v>
       </c>
       <c r="G12">
-        <v>17.60358714605995</v>
+        <v>22.52760939965125</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>34.61495348055151</v>
+      </c>
+      <c r="C13">
         <v>21.53346037439749</v>
-      </c>
-      <c r="C13">
-        <v>34.61495348055151</v>
       </c>
       <c r="D13">
         <v>4.643935450286309</v>
       </c>
       <c r="E13">
-        <v>13.79038047379756</v>
+        <v>22.16798277099785</v>
       </c>
       <c r="F13">
         <v>64.04163675520459</v>
       </c>
       <c r="G13">
-        <v>22.16798277099785</v>
+        <v>13.79038047379756</v>
       </c>
     </row>
   </sheetData>
